--- a/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:05:53+00:00</t>
+    <t>2026-09-14T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:56:03+00:00</t>
+    <t>2026-09-14T08:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:15:57+00:00</t>
+    <t>2026-10-14T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:44:38+00:00</t>
+    <t>2026-10-19T22:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-tnm-l-kategorie-werte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:30:48+00:00</t>
+    <t>2026-10-19T23:12:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
